--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2024_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2024_coquimbo.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 15:05</t>
+    <t xml:space="preserve">2026-09-24 01:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -579,7 +579,7 @@
         <v>-0.04</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0.69</v>
@@ -602,10 +602,10 @@
         <v>-0.09</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="4">
@@ -625,7 +625,7 @@
         <v>-0.04</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0.56</v>
@@ -648,7 +648,7 @@
         <v>0.1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>-0.42</v>
@@ -671,7 +671,7 @@
         <v>0.08</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>-0.5</v>
@@ -944,10 +944,10 @@
         <v>15</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0.57</v>
@@ -970,7 +970,7 @@
         <v>-0.54</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>1.39</v>
@@ -993,7 +993,7 @@
         <v>-0.33</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>1.26</v>
@@ -1013,13 +1013,13 @@
         <v>15</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.64</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="22">
@@ -1036,10 +1036,10 @@
         <v>15</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>-0.16</v>
@@ -1062,7 +1062,7 @@
         <v>0.06</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>-0.46</v>
@@ -1108,7 +1108,7 @@
         <v>-0.01</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0.54</v>
@@ -1131,7 +1131,7 @@
         <v>-0.53</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>1.39</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2024_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2024_coquimbo.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:54</t>
+    <t xml:space="preserve">2026-10-01 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2024_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_saldomigr_a_2024_coquimbo.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:12</t>
+    <t xml:space="preserve">2026-10-05 20:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
